--- a/JsonConverter/ExcelFiles/Engine.xlsx
+++ b/JsonConverter/ExcelFiles/Engine.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
   <si>
     <t xml:space="preserve">고유 ID</t>
   </si>
@@ -37,6 +37,9 @@
     <t xml:space="preserve">배의 관성 </t>
   </si>
   <si>
+    <t xml:space="preserve">엔진 표기용 Icon</t>
+  </si>
+  <si>
     <t xml:space="preserve">(name)</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
   </si>
   <si>
     <t xml:space="preserve">Acceleration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IconPath</t>
   </si>
   <si>
     <t xml:space="preserve">Engine_0001</t>
@@ -161,7 +167,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -193,6 +199,12 @@
       <name val="&quot;맑은 고딕&quot;"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF008000"/>
+      <name val="DotumChe"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -270,7 +282,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -283,7 +295,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -295,7 +311,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -553,12 +569,17 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
+  <dimension ref="A1:N1000"/>
   <sheetFormatPr defaultColWidth="11.53125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="46.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46.52"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -578,530 +599,547 @@
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="F3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="F6" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E7" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="F7" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E9" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F9" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="G9" s="5"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E10" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F10" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="G10" s="5"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E13" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="F6" s="4" t="n">
+      <c r="F13" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0.5</v>
-      </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="0"/>
-      <c r="F17" s="0"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/JsonConverter/ExcelFiles/Engine.xlsx
+++ b/JsonConverter/ExcelFiles/Engine.xlsx
@@ -94,7 +94,7 @@
     <t xml:space="preserve">엔진 3</t>
   </si>
   <si>
-    <t xml:space="preserve">위력이 상승한 포</t>
+    <t xml:space="preserve">조금 좋은 엔진</t>
   </si>
   <si>
     <t xml:space="preserve">Engine_0004</t>
@@ -103,7 +103,7 @@
     <t xml:space="preserve">엔진 4</t>
   </si>
   <si>
-    <t xml:space="preserve">중장거리에서 강력한 포</t>
+    <t xml:space="preserve">가장 좋은 엔진</t>
   </si>
   <si>
     <t xml:space="preserve">Engine_0005</t>
@@ -112,52 +112,52 @@
     <t xml:space="preserve">엔진 5</t>
   </si>
   <si>
-    <t xml:space="preserve">최고의 관통력을 자랑하는 포</t>
+    <t xml:space="preserve">최고의 엔진</t>
   </si>
   <si>
     <t xml:space="preserve">Engine_0006</t>
   </si>
   <si>
-    <t xml:space="preserve">해양생물 이동력 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해양생물의 이동력 1 이다</t>
+    <t xml:space="preserve">해양생물1 이동력</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해양생물1 이동력이다</t>
   </si>
   <si>
     <t xml:space="preserve">Engine_0007</t>
   </si>
   <si>
-    <t xml:space="preserve">해양생물 이동력 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해양생물의 이동력 2 이다</t>
+    <t xml:space="preserve">해양생물2 이동력</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해양생물2 이동력이다</t>
   </si>
   <si>
     <t xml:space="preserve">Engine_0008</t>
   </si>
   <si>
-    <t xml:space="preserve">해양생물 이동력 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해양생물의 이동력 3 이다</t>
+    <t xml:space="preserve">해양생물3 이동력</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해양생물3 이동력이다</t>
   </si>
   <si>
     <t xml:space="preserve">Engine_0009</t>
   </si>
   <si>
-    <t xml:space="preserve">해양생물 이동력 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해양생물의 이동력 4 이다</t>
+    <t xml:space="preserve">해양생물4 이동력</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해양생물4 이동력이다</t>
   </si>
   <si>
     <t xml:space="preserve">Engine_0010</t>
   </si>
   <si>
-    <t xml:space="preserve">해양생물 이동력 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해양생물의 이동력 5 이다</t>
+    <t xml:space="preserve">해양생물5 이동력</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해양생물5 이동력이다</t>
   </si>
 </sst>
 </file>
@@ -205,6 +205,7 @@
       <color rgb="FF008000"/>
       <name val="DotumChe"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -579,7 +580,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/JsonConverter/ExcelFiles/Engine.xlsx
+++ b/JsonConverter/ExcelFiles/Engine.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
   <si>
     <t xml:space="preserve">고유 ID</t>
   </si>
@@ -37,6 +37,9 @@
     <t xml:space="preserve">배의 관성 </t>
   </si>
   <si>
+    <t xml:space="preserve">가격</t>
+  </si>
+  <si>
     <t xml:space="preserve">엔진 표기용 Icon</t>
   </si>
   <si>
@@ -49,6 +52,9 @@
     <t xml:space="preserve">float</t>
   </si>
   <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
     <t xml:space="preserve">Id</t>
   </si>
   <si>
@@ -67,6 +73,9 @@
     <t xml:space="preserve">Acceleration</t>
   </si>
   <si>
+    <t xml:space="preserve">Price</t>
+  </si>
+  <si>
     <t xml:space="preserve">IconPath</t>
   </si>
   <si>
@@ -79,6 +88,9 @@
     <t xml:space="preserve">기초적인 엔진</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Icon_Engine_0001</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engine_0002</t>
   </si>
   <si>
@@ -88,6 +100,9 @@
     <t xml:space="preserve">표준적인 엔진</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Icon_Engine_0002</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engine_0003</t>
   </si>
   <si>
@@ -97,6 +112,9 @@
     <t xml:space="preserve">조금 좋은 엔진</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Icon_Engine_0003</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engine_0004</t>
   </si>
   <si>
@@ -106,6 +124,9 @@
     <t xml:space="preserve">가장 좋은 엔진</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Icon_Engine_0004</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engine_0005</t>
   </si>
   <si>
@@ -115,6 +136,9 @@
     <t xml:space="preserve">최고의 엔진</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Icon_Engine_0005</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engine_0006</t>
   </si>
   <si>
@@ -124,6 +148,9 @@
     <t xml:space="preserve">해양생물1 이동력이다</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Icon_Engine_0006</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engine_0007</t>
   </si>
   <si>
@@ -133,6 +160,9 @@
     <t xml:space="preserve">해양생물2 이동력이다</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Icon_Engine_0007</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engine_0008</t>
   </si>
   <si>
@@ -142,6 +172,9 @@
     <t xml:space="preserve">해양생물3 이동력이다</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Icon_Engine_0008</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engine_0009</t>
   </si>
   <si>
@@ -151,6 +184,9 @@
     <t xml:space="preserve">해양생물4 이동력이다</t>
   </si>
   <si>
+    <t xml:space="preserve">Icon/Icon_Engine_0009</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engine_0010</t>
   </si>
   <si>
@@ -158,6 +194,9 @@
   </si>
   <si>
     <t xml:space="preserve">해양생물5 이동력이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Icon/Icon_Engine_0010</t>
   </si>
 </sst>
 </file>
@@ -167,7 +206,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -212,6 +251,13 @@
       <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
       <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
       <charset val="129"/>
     </font>
     <font>
@@ -283,7 +329,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -308,11 +354,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -570,7 +620,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N1000"/>
+  <dimension ref="A1:O1000"/>
   <sheetFormatPr defaultColWidth="11.53125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.1"/>
@@ -579,8 +629,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="14.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -600,65 +649,74 @@
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>0.1</v>
@@ -669,24 +727,29 @@
       <c r="F4" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
+      <c r="G4" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0.2</v>
@@ -697,24 +760,29 @@
       <c r="F5" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
+      <c r="G5" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0.4</v>
@@ -725,24 +793,29 @@
       <c r="F6" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
+      <c r="G6" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>0.6</v>
@@ -753,24 +826,29 @@
       <c r="F7" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
+      <c r="G7" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>0.8</v>
@@ -781,24 +859,29 @@
       <c r="F8" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
+      <c r="G8" s="5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>0.1</v>
@@ -809,24 +892,29 @@
       <c r="F9" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
+      <c r="G9" s="5" t="n">
+        <v>99999</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>0.2</v>
@@ -837,24 +925,29 @@
       <c r="F10" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
+      <c r="G10" s="5" t="n">
+        <v>99999</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>0.4</v>
@@ -865,24 +958,29 @@
       <c r="F11" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
+      <c r="G11" s="5" t="n">
+        <v>99999</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>0.6</v>
@@ -893,24 +991,29 @@
       <c r="F12" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
+      <c r="G12" s="5" t="n">
+        <v>99999</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>0.8</v>
@@ -921,14 +1024,19 @@
       <c r="F13" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
+      <c r="G13" s="5" t="n">
+        <v>99999</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -938,13 +1046,14 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -954,193 +1063,214 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
